--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.11956319238421</v>
+        <v>8.306929018762434</v>
       </c>
       <c r="D2" t="n">
-        <v>51.38371195765723</v>
+        <v>8.349853193119301</v>
       </c>
       <c r="E2" t="n">
-        <v>5.562886398455313</v>
+        <v>0.9039690397489882</v>
       </c>
       <c r="F2" t="n">
-        <v>5.50207361099289</v>
+        <v>0.8940869617863448</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.11853216597817</v>
+        <v>7.006761476971453</v>
       </c>
       <c r="D3" t="n">
-        <v>42.98496550179185</v>
+        <v>6.985056894041175</v>
       </c>
       <c r="E3" t="n">
-        <v>5.562886398455313</v>
+        <v>0.9039690397489882</v>
       </c>
       <c r="F3" t="n">
-        <v>5.50207361099289</v>
+        <v>0.8940869617863448</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>56.67118355318351</v>
+        <v>9.20906732739232</v>
       </c>
       <c r="D4" t="n">
-        <v>56.31250703289994</v>
+        <v>9.15078239284624</v>
       </c>
       <c r="E4" t="n">
-        <v>5.562886398455313</v>
+        <v>0.9039690397489882</v>
       </c>
       <c r="F4" t="n">
-        <v>5.50207361099289</v>
+        <v>0.8940869617863448</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
